--- a/data/trans_bre/IP16B10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B10-Estudios-trans_bre.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,33</t>
+          <t>0,0; 60,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,48</t>
+          <t>0,0; 60,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 197,16</t>
+          <t>0,0; 150,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B10-Estudios-trans_bre.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,21</t>
+          <t>0,0; 62,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 150,01</t>
+          <t>0,0; 169,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
